--- a/2-Section- Basic Excel/data/08 E-Commerce Orders.xlsx
+++ b/2-Section- Basic Excel/data/08 E-Commerce Orders.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29902"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumit\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a6ce4a7617f1ad9/Desktop/courses/Data Analytics/2-Section- Basic Excel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32B112D0-A8A8-43D3-8B30-03F45CAD7F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{32B112D0-A8A8-43D3-8B30-03F45CAD7F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13156F49-D238-4AD9-A277-A06D1C4F4C0F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{E58E7B76-BBA2-4FEA-9902-8DB1E54E41DD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E58E7B76-BBA2-4FEA-9902-8DB1E54E41DD}"/>
   </bookViews>
   <sheets>
     <sheet name="E-Commerce Orders" sheetId="1" r:id="rId1"/>
@@ -5687,23 +5687,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2433D4D-222C-4D7E-9CFE-8FD0E76428CA}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L1001"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="26.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="30.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -5931,7 +5931,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -6159,7 +6159,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>70</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>76</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -6501,7 +6501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>81</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>84</v>
       </c>
@@ -6577,7 +6577,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>86</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -6653,7 +6653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>92</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>95</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>97</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>101</v>
       </c>
@@ -6843,7 +6843,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>103</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>106</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>109</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>112</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>114</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>119</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -7147,7 +7147,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>123</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>125</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>127</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>131</v>
       </c>
@@ -7337,7 +7337,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>134</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>137</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>139</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>142</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>144</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>146</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>149</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>152</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>155</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>157</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>163</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -7869,7 +7869,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>169</v>
       </c>
@@ -7945,7 +7945,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>171</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>173</v>
       </c>
@@ -8021,7 +8021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>175</v>
       </c>
@@ -8059,7 +8059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>180</v>
       </c>
@@ -8135,7 +8135,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>182</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>185</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>188</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>190</v>
       </c>
@@ -8287,7 +8287,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>192</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>194</v>
       </c>
@@ -8363,7 +8363,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>196</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>198</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>200</v>
       </c>
@@ -8477,7 +8477,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>202</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>204</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>206</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>209</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>212</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>215</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>217</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>218</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>220</v>
       </c>
@@ -8819,7 +8819,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>223</v>
       </c>
@@ -8857,7 +8857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>225</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>228</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>230</v>
       </c>
@@ -8971,7 +8971,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>233</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>235</v>
       </c>
@@ -9047,7 +9047,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>236</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>238</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>240</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>242</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>244</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>247</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>249</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>251</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>254</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>255</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>257</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>259</v>
       </c>
@@ -9503,7 +9503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>261</v>
       </c>
@@ -9541,7 +9541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>263</v>
       </c>
@@ -9579,7 +9579,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>265</v>
       </c>
@@ -9617,7 +9617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>267</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>270</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>272</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>274</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>276</v>
       </c>
@@ -9807,7 +9807,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>278</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>280</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>282</v>
       </c>
@@ -9921,7 +9921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>284</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>287</v>
       </c>
@@ -9997,7 +9997,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>289</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>292</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>293</v>
       </c>
@@ -10111,7 +10111,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>295</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>297</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>299</v>
       </c>
@@ -10225,7 +10225,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>301</v>
       </c>
@@ -10263,7 +10263,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>303</v>
       </c>
@@ -10301,7 +10301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>305</v>
       </c>
@@ -10339,7 +10339,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>307</v>
       </c>
@@ -10377,7 +10377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>310</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>311</v>
       </c>
@@ -10453,7 +10453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>313</v>
       </c>
@@ -10491,7 +10491,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>315</v>
       </c>
@@ -10529,7 +10529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>317</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>319</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>321</v>
       </c>
@@ -10643,7 +10643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>323</v>
       </c>
@@ -10681,7 +10681,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>325</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>327</v>
       </c>
@@ -10757,7 +10757,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>329</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>331</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>333</v>
       </c>
@@ -10871,7 +10871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>335</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>337</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>339</v>
       </c>
@@ -10985,7 +10985,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>341</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>343</v>
       </c>
@@ -11061,7 +11061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>345</v>
       </c>
@@ -11099,7 +11099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>347</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>348</v>
       </c>
@@ -11175,7 +11175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>350</v>
       </c>
@@ -11213,7 +11213,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>352</v>
       </c>
@@ -11251,7 +11251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>354</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>356</v>
       </c>
@@ -11327,7 +11327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>358</v>
       </c>
@@ -11365,7 +11365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>360</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>362</v>
       </c>
@@ -11441,7 +11441,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>364</v>
       </c>
@@ -11479,7 +11479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>366</v>
       </c>
@@ -11517,7 +11517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>368</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>370</v>
       </c>
@@ -11593,7 +11593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>371</v>
       </c>
@@ -11631,7 +11631,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>373</v>
       </c>
@@ -11669,7 +11669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>375</v>
       </c>
@@ -11707,7 +11707,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>377</v>
       </c>
@@ -11745,7 +11745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>379</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>381</v>
       </c>
@@ -11821,7 +11821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>383</v>
       </c>
@@ -11859,7 +11859,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>385</v>
       </c>
@@ -11897,7 +11897,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>387</v>
       </c>
@@ -11935,7 +11935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>389</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>391</v>
       </c>
@@ -12011,7 +12011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>393</v>
       </c>
@@ -12049,7 +12049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>395</v>
       </c>
@@ -12087,7 +12087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>397</v>
       </c>
@@ -12125,7 +12125,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>399</v>
       </c>
@@ -12163,7 +12163,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>401</v>
       </c>
@@ -12201,7 +12201,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>403</v>
       </c>
@@ -12239,7 +12239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>405</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>406</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>408</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>409</v>
       </c>
@@ -12391,7 +12391,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>410</v>
       </c>
@@ -12429,7 +12429,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>412</v>
       </c>
@@ -12467,7 +12467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>414</v>
       </c>
@@ -12505,7 +12505,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>416</v>
       </c>
@@ -12543,7 +12543,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>418</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>420</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>422</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>424</v>
       </c>
@@ -12695,7 +12695,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>426</v>
       </c>
@@ -12733,7 +12733,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>428</v>
       </c>
@@ -12771,7 +12771,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>430</v>
       </c>
@@ -12809,7 +12809,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>432</v>
       </c>
@@ -12847,7 +12847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>434</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>436</v>
       </c>
@@ -12923,7 +12923,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>438</v>
       </c>
@@ -12961,7 +12961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>440</v>
       </c>
@@ -12999,7 +12999,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>442</v>
       </c>
@@ -13037,7 +13037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>444</v>
       </c>
@@ -13075,7 +13075,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>446</v>
       </c>
@@ -13113,7 +13113,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>448</v>
       </c>
@@ -13151,7 +13151,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>450</v>
       </c>
@@ -13189,7 +13189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>452</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>454</v>
       </c>
@@ -13265,7 +13265,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>456</v>
       </c>
@@ -13303,7 +13303,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>458</v>
       </c>
@@ -13341,7 +13341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>461</v>
       </c>
@@ -13379,7 +13379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>462</v>
       </c>
@@ -13417,7 +13417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>464</v>
       </c>
@@ -13455,7 +13455,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>466</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>468</v>
       </c>
@@ -13531,7 +13531,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>470</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>472</v>
       </c>
@@ -13607,7 +13607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>474</v>
       </c>
@@ -13645,7 +13645,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>476</v>
       </c>
@@ -13683,7 +13683,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>478</v>
       </c>
@@ -13721,7 +13721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>480</v>
       </c>
@@ -13759,7 +13759,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>482</v>
       </c>
@@ -13797,7 +13797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>484</v>
       </c>
@@ -13835,7 +13835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>486</v>
       </c>
@@ -13873,7 +13873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>488</v>
       </c>
@@ -13911,7 +13911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>489</v>
       </c>
@@ -13949,7 +13949,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>491</v>
       </c>
@@ -13987,7 +13987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>493</v>
       </c>
@@ -14025,7 +14025,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>495</v>
       </c>
@@ -14063,7 +14063,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>497</v>
       </c>
@@ -14101,7 +14101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>499</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>500</v>
       </c>
@@ -14177,7 +14177,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>503</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>505</v>
       </c>
@@ -14253,7 +14253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>507</v>
       </c>
@@ -14291,7 +14291,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>509</v>
       </c>
@@ -14329,7 +14329,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>511</v>
       </c>
@@ -14367,7 +14367,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>513</v>
       </c>
@@ -14405,7 +14405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>515</v>
       </c>
@@ -14443,7 +14443,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>517</v>
       </c>
@@ -14481,7 +14481,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>519</v>
       </c>
@@ -14519,7 +14519,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>521</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>522</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>524</v>
       </c>
@@ -14633,7 +14633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>526</v>
       </c>
@@ -14671,7 +14671,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>528</v>
       </c>
@@ -14709,7 +14709,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>530</v>
       </c>
@@ -14747,7 +14747,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>532</v>
       </c>
@@ -14785,7 +14785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>534</v>
       </c>
@@ -14823,7 +14823,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>536</v>
       </c>
@@ -14861,7 +14861,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>538</v>
       </c>
@@ -14899,7 +14899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>540</v>
       </c>
@@ -14937,7 +14937,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>542</v>
       </c>
@@ -14975,7 +14975,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>544</v>
       </c>
@@ -15013,7 +15013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>545</v>
       </c>
@@ -15051,7 +15051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>546</v>
       </c>
@@ -15089,7 +15089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>548</v>
       </c>
@@ -15127,7 +15127,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>549</v>
       </c>
@@ -15165,7 +15165,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>551</v>
       </c>
@@ -15203,7 +15203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>553</v>
       </c>
@@ -15241,7 +15241,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>555</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>557</v>
       </c>
@@ -15317,7 +15317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>558</v>
       </c>
@@ -15355,7 +15355,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>560</v>
       </c>
@@ -15393,7 +15393,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>561</v>
       </c>
@@ -15431,7 +15431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>562</v>
       </c>
@@ -15469,7 +15469,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>564</v>
       </c>
@@ -15507,7 +15507,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>566</v>
       </c>
@@ -15545,7 +15545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>568</v>
       </c>
@@ -15583,7 +15583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>570</v>
       </c>
@@ -15621,7 +15621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>572</v>
       </c>
@@ -15659,7 +15659,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>574</v>
       </c>
@@ -15697,7 +15697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>576</v>
       </c>
@@ -15735,7 +15735,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>578</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>580</v>
       </c>
@@ -15811,7 +15811,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>582</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>583</v>
       </c>
@@ -15887,7 +15887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>585</v>
       </c>
@@ -15925,7 +15925,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>587</v>
       </c>
@@ -15963,7 +15963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>589</v>
       </c>
@@ -16001,7 +16001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>591</v>
       </c>
@@ -16039,7 +16039,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>592</v>
       </c>
@@ -16077,7 +16077,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>594</v>
       </c>
@@ -16115,7 +16115,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>596</v>
       </c>
@@ -16153,7 +16153,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>598</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>600</v>
       </c>
@@ -16229,7 +16229,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>601</v>
       </c>
@@ -16267,7 +16267,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>602</v>
       </c>
@@ -16305,7 +16305,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>604</v>
       </c>
@@ -16343,7 +16343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>606</v>
       </c>
@@ -16381,7 +16381,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>608</v>
       </c>
@@ -16419,7 +16419,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>610</v>
       </c>
@@ -16457,7 +16457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>612</v>
       </c>
@@ -16495,7 +16495,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>613</v>
       </c>
@@ -16533,7 +16533,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>614</v>
       </c>
@@ -16571,7 +16571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>615</v>
       </c>
@@ -16609,7 +16609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>617</v>
       </c>
@@ -16647,7 +16647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>619</v>
       </c>
@@ -16685,7 +16685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>620</v>
       </c>
@@ -16723,7 +16723,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>622</v>
       </c>
@@ -16761,7 +16761,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>624</v>
       </c>
@@ -16799,7 +16799,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>625</v>
       </c>
@@ -16837,7 +16837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>627</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>628</v>
       </c>
@@ -16913,7 +16913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>630</v>
       </c>
@@ -16951,7 +16951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>632</v>
       </c>
@@ -16989,7 +16989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>634</v>
       </c>
@@ -17027,7 +17027,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>636</v>
       </c>
@@ -17065,7 +17065,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>638</v>
       </c>
@@ -17103,7 +17103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>640</v>
       </c>
@@ -17141,7 +17141,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>641</v>
       </c>
@@ -17179,7 +17179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>643</v>
       </c>
@@ -17217,7 +17217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>644</v>
       </c>
@@ -17255,7 +17255,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>646</v>
       </c>
@@ -17293,7 +17293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>648</v>
       </c>
@@ -17331,7 +17331,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>650</v>
       </c>
@@ -17369,7 +17369,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>652</v>
       </c>
@@ -17407,7 +17407,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>654</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>656</v>
       </c>
@@ -17483,7 +17483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>657</v>
       </c>
@@ -17521,7 +17521,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>659</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>661</v>
       </c>
@@ -17597,7 +17597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>663</v>
       </c>
@@ -17635,7 +17635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>665</v>
       </c>
@@ -17673,7 +17673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>667</v>
       </c>
@@ -17711,7 +17711,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>669</v>
       </c>
@@ -17749,7 +17749,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>671</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>673</v>
       </c>
@@ -17825,7 +17825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>675</v>
       </c>
@@ -17863,7 +17863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>676</v>
       </c>
@@ -17901,7 +17901,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>677</v>
       </c>
@@ -17939,7 +17939,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>679</v>
       </c>
@@ -17977,7 +17977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>680</v>
       </c>
@@ -18015,7 +18015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>682</v>
       </c>
@@ -18053,7 +18053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>684</v>
       </c>
@@ -18091,7 +18091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>685</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>687</v>
       </c>
@@ -18167,7 +18167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>689</v>
       </c>
@@ -18205,7 +18205,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>691</v>
       </c>
@@ -18243,7 +18243,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>692</v>
       </c>
@@ -18281,7 +18281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>694</v>
       </c>
@@ -18319,7 +18319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>696</v>
       </c>
@@ -18357,7 +18357,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>697</v>
       </c>
@@ -18395,7 +18395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>699</v>
       </c>
@@ -18433,7 +18433,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>701</v>
       </c>
@@ -18471,7 +18471,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>703</v>
       </c>
@@ -18509,7 +18509,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>705</v>
       </c>
@@ -18547,7 +18547,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>707</v>
       </c>
@@ -18585,7 +18585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>709</v>
       </c>
@@ -18623,7 +18623,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>710</v>
       </c>
@@ -18661,7 +18661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>712</v>
       </c>
@@ -18699,7 +18699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>714</v>
       </c>
@@ -18737,7 +18737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>715</v>
       </c>
@@ -18775,7 +18775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>716</v>
       </c>
@@ -18813,7 +18813,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>718</v>
       </c>
@@ -18851,7 +18851,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>719</v>
       </c>
@@ -18889,7 +18889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>721</v>
       </c>
@@ -18927,7 +18927,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>722</v>
       </c>
@@ -18965,7 +18965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>723</v>
       </c>
@@ -19003,7 +19003,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>725</v>
       </c>
@@ -19041,7 +19041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>727</v>
       </c>
@@ -19079,7 +19079,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>728</v>
       </c>
@@ -19117,7 +19117,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>730</v>
       </c>
@@ -19155,7 +19155,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>731</v>
       </c>
@@ -19193,7 +19193,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>733</v>
       </c>
@@ -19231,7 +19231,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>735</v>
       </c>
@@ -19269,7 +19269,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>737</v>
       </c>
@@ -19307,7 +19307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>739</v>
       </c>
@@ -19345,7 +19345,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>740</v>
       </c>
@@ -19383,7 +19383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>742</v>
       </c>
@@ -19421,7 +19421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>744</v>
       </c>
@@ -19459,7 +19459,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>746</v>
       </c>
@@ -19497,7 +19497,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>747</v>
       </c>
@@ -19535,7 +19535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>748</v>
       </c>
@@ -19573,7 +19573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>750</v>
       </c>
@@ -19611,7 +19611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>752</v>
       </c>
@@ -19649,7 +19649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>753</v>
       </c>
@@ -19687,7 +19687,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>755</v>
       </c>
@@ -19725,7 +19725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>757</v>
       </c>
@@ -19763,7 +19763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>759</v>
       </c>
@@ -19801,7 +19801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>760</v>
       </c>
@@ -19839,7 +19839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>762</v>
       </c>
@@ -19877,7 +19877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>763</v>
       </c>
@@ -19915,7 +19915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>765</v>
       </c>
@@ -19953,7 +19953,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>767</v>
       </c>
@@ -19991,7 +19991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>769</v>
       </c>
@@ -20029,7 +20029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>771</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>772</v>
       </c>
@@ -20105,7 +20105,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>774</v>
       </c>
@@ -20143,7 +20143,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>776</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>778</v>
       </c>
@@ -20219,7 +20219,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>780</v>
       </c>
@@ -20257,7 +20257,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>782</v>
       </c>
@@ -20295,7 +20295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>784</v>
       </c>
@@ -20333,7 +20333,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>785</v>
       </c>
@@ -20371,7 +20371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>787</v>
       </c>
@@ -20409,7 +20409,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>789</v>
       </c>
@@ -20447,7 +20447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>790</v>
       </c>
@@ -20485,7 +20485,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>792</v>
       </c>
@@ -20523,7 +20523,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>794</v>
       </c>
@@ -20561,7 +20561,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>796</v>
       </c>
@@ -20599,7 +20599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>798</v>
       </c>
@@ -20637,7 +20637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>800</v>
       </c>
@@ -20675,7 +20675,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>802</v>
       </c>
@@ -20713,7 +20713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>804</v>
       </c>
@@ -20751,7 +20751,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>805</v>
       </c>
@@ -20789,7 +20789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>807</v>
       </c>
@@ -20827,7 +20827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>808</v>
       </c>
@@ -20865,7 +20865,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>809</v>
       </c>
@@ -20903,7 +20903,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>811</v>
       </c>
@@ -20941,7 +20941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>813</v>
       </c>
@@ -20979,7 +20979,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>815</v>
       </c>
@@ -21017,7 +21017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>816</v>
       </c>
@@ -21055,7 +21055,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>818</v>
       </c>
@@ -21093,7 +21093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>819</v>
       </c>
@@ -21131,7 +21131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>821</v>
       </c>
@@ -21169,7 +21169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>823</v>
       </c>
@@ -21207,7 +21207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>825</v>
       </c>
@@ -21245,7 +21245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>826</v>
       </c>
@@ -21283,7 +21283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>827</v>
       </c>
@@ -21321,7 +21321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>829</v>
       </c>
@@ -21359,7 +21359,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>830</v>
       </c>
@@ -21397,7 +21397,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>832</v>
       </c>
@@ -21435,7 +21435,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>834</v>
       </c>
@@ -21473,7 +21473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>835</v>
       </c>
@@ -21511,7 +21511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>837</v>
       </c>
@@ -21549,7 +21549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>839</v>
       </c>
@@ -21587,7 +21587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>841</v>
       </c>
@@ -21625,7 +21625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>843</v>
       </c>
@@ -21663,7 +21663,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>845</v>
       </c>
@@ -21701,7 +21701,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>847</v>
       </c>
@@ -21739,7 +21739,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>849</v>
       </c>
@@ -21777,7 +21777,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>851</v>
       </c>
@@ -21815,7 +21815,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>853</v>
       </c>
@@ -21853,7 +21853,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>854</v>
       </c>
@@ -21891,7 +21891,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>856</v>
       </c>
@@ -21929,7 +21929,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>858</v>
       </c>
@@ -21967,7 +21967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>860</v>
       </c>
@@ -22005,7 +22005,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>862</v>
       </c>
@@ -22043,7 +22043,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>864</v>
       </c>
@@ -22081,7 +22081,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>865</v>
       </c>
@@ -22119,7 +22119,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>867</v>
       </c>
@@ -22157,7 +22157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>869</v>
       </c>
@@ -22195,7 +22195,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>870</v>
       </c>
@@ -22233,7 +22233,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>872</v>
       </c>
@@ -22271,7 +22271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>873</v>
       </c>
@@ -22309,7 +22309,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>875</v>
       </c>
@@ -22347,7 +22347,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>877</v>
       </c>
@@ -22385,7 +22385,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>878</v>
       </c>
@@ -22423,7 +22423,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>880</v>
       </c>
@@ -22461,7 +22461,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>881</v>
       </c>
@@ -22499,7 +22499,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>883</v>
       </c>
@@ -22537,7 +22537,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>884</v>
       </c>
@@ -22575,7 +22575,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>885</v>
       </c>
@@ -22613,7 +22613,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>886</v>
       </c>
@@ -22651,7 +22651,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>888</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>890</v>
       </c>
@@ -22727,7 +22727,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>891</v>
       </c>
@@ -22765,7 +22765,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>893</v>
       </c>
@@ -22803,7 +22803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>895</v>
       </c>
@@ -22841,7 +22841,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>897</v>
       </c>
@@ -22879,7 +22879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>899</v>
       </c>
@@ -22917,7 +22917,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>901</v>
       </c>
@@ -22955,7 +22955,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>902</v>
       </c>
@@ -22993,7 +22993,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>904</v>
       </c>
@@ -23031,7 +23031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>906</v>
       </c>
@@ -23069,7 +23069,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>908</v>
       </c>
@@ -23107,7 +23107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>910</v>
       </c>
@@ -23145,7 +23145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>912</v>
       </c>
@@ -23183,7 +23183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>913</v>
       </c>
@@ -23221,7 +23221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>915</v>
       </c>
@@ -23259,7 +23259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>917</v>
       </c>
@@ -23297,7 +23297,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>919</v>
       </c>
@@ -23335,7 +23335,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>921</v>
       </c>
@@ -23373,7 +23373,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>923</v>
       </c>
@@ -23411,7 +23411,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>924</v>
       </c>
@@ -23449,7 +23449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>926</v>
       </c>
@@ -23487,7 +23487,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>927</v>
       </c>
@@ -23525,7 +23525,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>928</v>
       </c>
@@ -23563,7 +23563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>930</v>
       </c>
@@ -23601,7 +23601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>932</v>
       </c>
@@ -23639,7 +23639,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>934</v>
       </c>
@@ -23677,7 +23677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>936</v>
       </c>
@@ -23715,7 +23715,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>938</v>
       </c>
@@ -23753,7 +23753,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>940</v>
       </c>
@@ -23791,7 +23791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>942</v>
       </c>
@@ -23829,7 +23829,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>944</v>
       </c>
@@ -23867,7 +23867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>946</v>
       </c>
@@ -23905,7 +23905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>948</v>
       </c>
@@ -23943,7 +23943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>950</v>
       </c>
@@ -23981,7 +23981,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>951</v>
       </c>
@@ -24019,7 +24019,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>953</v>
       </c>
@@ -24057,7 +24057,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>955</v>
       </c>
@@ -24095,7 +24095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>957</v>
       </c>
@@ -24133,7 +24133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>958</v>
       </c>
@@ -24171,7 +24171,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>960</v>
       </c>
@@ -24209,7 +24209,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>962</v>
       </c>
@@ -24247,7 +24247,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>963</v>
       </c>
@@ -24285,7 +24285,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>964</v>
       </c>
@@ -24323,7 +24323,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>966</v>
       </c>
@@ -24361,7 +24361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>968</v>
       </c>
@@ -24399,7 +24399,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>969</v>
       </c>
@@ -24437,7 +24437,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>970</v>
       </c>
@@ -24475,7 +24475,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>971</v>
       </c>
@@ -24513,7 +24513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>973</v>
       </c>
@@ -24551,7 +24551,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>974</v>
       </c>
@@ -24589,7 +24589,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>976</v>
       </c>
@@ -24627,7 +24627,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>978</v>
       </c>
@@ -24665,7 +24665,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>979</v>
       </c>
@@ -24703,7 +24703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>981</v>
       </c>
@@ -24741,7 +24741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>982</v>
       </c>
@@ -24779,7 +24779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>983</v>
       </c>
@@ -24817,7 +24817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>984</v>
       </c>
@@ -24855,7 +24855,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>985</v>
       </c>
@@ -24893,7 +24893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>987</v>
       </c>
@@ -24931,7 +24931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>989</v>
       </c>
@@ -24969,7 +24969,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>991</v>
       </c>
@@ -25007,7 +25007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>992</v>
       </c>
@@ -25045,7 +25045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>993</v>
       </c>
@@ -25083,7 +25083,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>995</v>
       </c>
@@ -25121,7 +25121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>997</v>
       </c>
@@ -25159,7 +25159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>998</v>
       </c>
@@ -25197,7 +25197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>999</v>
       </c>
@@ -25235,7 +25235,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>1000</v>
       </c>
@@ -25273,7 +25273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>1002</v>
       </c>
@@ -25311,7 +25311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>1004</v>
       </c>
@@ -25349,7 +25349,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>1005</v>
       </c>
@@ -25387,7 +25387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>1006</v>
       </c>
@@ -25425,7 +25425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>1007</v>
       </c>
@@ -25463,7 +25463,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>1009</v>
       </c>
@@ -25501,7 +25501,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>1011</v>
       </c>
@@ -25539,7 +25539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>1012</v>
       </c>
@@ -25577,7 +25577,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>1014</v>
       </c>
@@ -25615,7 +25615,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>1016</v>
       </c>
@@ -25653,7 +25653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>1018</v>
       </c>
@@ -25691,7 +25691,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>1019</v>
       </c>
@@ -25729,7 +25729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>1020</v>
       </c>
@@ -25767,7 +25767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>1021</v>
       </c>
@@ -25805,7 +25805,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>1022</v>
       </c>
@@ -25843,7 +25843,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>1024</v>
       </c>
@@ -25881,7 +25881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>1025</v>
       </c>
@@ -25919,7 +25919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>1027</v>
       </c>
@@ -25957,7 +25957,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>1029</v>
       </c>
@@ -25995,7 +25995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>1031</v>
       </c>
@@ -26033,7 +26033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>1033</v>
       </c>
@@ -26071,7 +26071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>1035</v>
       </c>
@@ -26109,7 +26109,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>1037</v>
       </c>
@@ -26147,7 +26147,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>1039</v>
       </c>
@@ -26185,7 +26185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>1040</v>
       </c>
@@ -26223,7 +26223,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>1042</v>
       </c>
@@ -26261,7 +26261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>1044</v>
       </c>
@@ -26299,7 +26299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>1046</v>
       </c>
@@ -26337,7 +26337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>1048</v>
       </c>
@@ -26375,7 +26375,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>1049</v>
       </c>
@@ -26413,7 +26413,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>1051</v>
       </c>
@@ -26451,7 +26451,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>1052</v>
       </c>
@@ -26489,7 +26489,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>1053</v>
       </c>
@@ -26527,7 +26527,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>1054</v>
       </c>
@@ -26565,7 +26565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>1056</v>
       </c>
@@ -26603,7 +26603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>1057</v>
       </c>
@@ -26641,7 +26641,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>1059</v>
       </c>
@@ -26679,7 +26679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>1061</v>
       </c>
@@ -26717,7 +26717,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>1063</v>
       </c>
@@ -26755,7 +26755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>1065</v>
       </c>
@@ -26793,7 +26793,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>1066</v>
       </c>
@@ -26831,7 +26831,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>1067</v>
       </c>
@@ -26869,7 +26869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>1069</v>
       </c>
@@ -26907,7 +26907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>1070</v>
       </c>
@@ -26945,7 +26945,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>1071</v>
       </c>
@@ -26983,7 +26983,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>1073</v>
       </c>
@@ -27021,7 +27021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>1075</v>
       </c>
@@ -27059,7 +27059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>1077</v>
       </c>
@@ -27097,7 +27097,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>1079</v>
       </c>
@@ -27135,7 +27135,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>1081</v>
       </c>
@@ -27173,7 +27173,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>1083</v>
       </c>
@@ -27211,7 +27211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>1084</v>
       </c>
@@ -27249,7 +27249,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>1086</v>
       </c>
@@ -27287,7 +27287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>1088</v>
       </c>
@@ -27325,7 +27325,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>1090</v>
       </c>
@@ -27363,7 +27363,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>1091</v>
       </c>
@@ -27401,7 +27401,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>1093</v>
       </c>
@@ -27439,7 +27439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>1095</v>
       </c>
@@ -27477,7 +27477,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>1097</v>
       </c>
@@ -27515,7 +27515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>1099</v>
       </c>
@@ -27553,7 +27553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>1101</v>
       </c>
@@ -27591,7 +27591,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>1102</v>
       </c>
@@ -27629,7 +27629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>1104</v>
       </c>
@@ -27667,7 +27667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>1105</v>
       </c>
@@ -27705,7 +27705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>1106</v>
       </c>
@@ -27743,7 +27743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>1108</v>
       </c>
@@ -27781,7 +27781,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>1109</v>
       </c>
@@ -27819,7 +27819,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>1110</v>
       </c>
@@ -27857,7 +27857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>1112</v>
       </c>
@@ -27895,7 +27895,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>1114</v>
       </c>
@@ -27933,7 +27933,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>1116</v>
       </c>
@@ -27971,7 +27971,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>1117</v>
       </c>
@@ -28009,7 +28009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>1119</v>
       </c>
@@ -28047,7 +28047,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>1121</v>
       </c>
@@ -28085,7 +28085,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>1122</v>
       </c>
@@ -28123,7 +28123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>1124</v>
       </c>
@@ -28161,7 +28161,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>1126</v>
       </c>
@@ -28199,7 +28199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>1128</v>
       </c>
@@ -28237,7 +28237,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>1130</v>
       </c>
@@ -28275,7 +28275,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>1132</v>
       </c>
@@ -28313,7 +28313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>1134</v>
       </c>
@@ -28351,7 +28351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>1136</v>
       </c>
@@ -28389,7 +28389,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>1137</v>
       </c>
@@ -28427,7 +28427,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>1139</v>
       </c>
@@ -28465,7 +28465,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>1140</v>
       </c>
@@ -28503,7 +28503,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>1142</v>
       </c>
@@ -28541,7 +28541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>1144</v>
       </c>
@@ -28579,7 +28579,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>1145</v>
       </c>
@@ -28617,7 +28617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>1147</v>
       </c>
@@ -28655,7 +28655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>1148</v>
       </c>
@@ -28693,7 +28693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>1150</v>
       </c>
@@ -28731,7 +28731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>1152</v>
       </c>
@@ -28769,7 +28769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>1153</v>
       </c>
@@ -28807,7 +28807,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>1154</v>
       </c>
@@ -28845,7 +28845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>1155</v>
       </c>
@@ -28883,7 +28883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>1156</v>
       </c>
@@ -28921,7 +28921,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>1157</v>
       </c>
@@ -28959,7 +28959,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>1159</v>
       </c>
@@ -28997,7 +28997,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>1160</v>
       </c>
@@ -29035,7 +29035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>1161</v>
       </c>
@@ -29073,7 +29073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>1163</v>
       </c>
@@ -29111,7 +29111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>1164</v>
       </c>
@@ -29149,7 +29149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>1165</v>
       </c>
@@ -29187,7 +29187,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>1167</v>
       </c>
@@ -29225,7 +29225,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>1169</v>
       </c>
@@ -29263,7 +29263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>1171</v>
       </c>
@@ -29301,7 +29301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>1173</v>
       </c>
@@ -29339,7 +29339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>1174</v>
       </c>
@@ -29377,7 +29377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>1175</v>
       </c>
@@ -29415,7 +29415,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>1176</v>
       </c>
@@ -29453,7 +29453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>1177</v>
       </c>
@@ -29491,7 +29491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>1179</v>
       </c>
@@ -29529,7 +29529,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>1181</v>
       </c>
@@ -29567,7 +29567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>1183</v>
       </c>
@@ -29605,7 +29605,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>1185</v>
       </c>
@@ -29643,7 +29643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>1187</v>
       </c>
@@ -29681,7 +29681,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>1189</v>
       </c>
@@ -29719,7 +29719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>1191</v>
       </c>
@@ -29757,7 +29757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>1193</v>
       </c>
@@ -29795,7 +29795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>1194</v>
       </c>
@@ -29833,7 +29833,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>1195</v>
       </c>
@@ -29871,7 +29871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>1196</v>
       </c>
@@ -29909,7 +29909,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>1198</v>
       </c>
@@ -29947,7 +29947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>1199</v>
       </c>
@@ -29985,7 +29985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>1200</v>
       </c>
@@ -30023,7 +30023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>1201</v>
       </c>
@@ -30061,7 +30061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>1203</v>
       </c>
@@ -30099,7 +30099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>1205</v>
       </c>
@@ -30137,7 +30137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>1207</v>
       </c>
@@ -30175,7 +30175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>1208</v>
       </c>
@@ -30213,7 +30213,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>1210</v>
       </c>
@@ -30251,7 +30251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>1211</v>
       </c>
@@ -30289,7 +30289,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>1213</v>
       </c>
@@ -30327,7 +30327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>1215</v>
       </c>
@@ -30365,7 +30365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>1217</v>
       </c>
@@ -30403,7 +30403,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>1218</v>
       </c>
@@ -30441,7 +30441,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>1219</v>
       </c>
@@ -30479,7 +30479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>1221</v>
       </c>
@@ -30517,7 +30517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>1222</v>
       </c>
@@ -30555,7 +30555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>1224</v>
       </c>
@@ -30593,7 +30593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>1225</v>
       </c>
@@ -30631,7 +30631,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>1226</v>
       </c>
@@ -30669,7 +30669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>1228</v>
       </c>
@@ -30707,7 +30707,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>1230</v>
       </c>
@@ -30745,7 +30745,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>1231</v>
       </c>
@@ -30783,7 +30783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>1232</v>
       </c>
@@ -30821,7 +30821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>1234</v>
       </c>
@@ -30859,7 +30859,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>1236</v>
       </c>
@@ -30897,7 +30897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>1238</v>
       </c>
@@ -30935,7 +30935,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>1239</v>
       </c>
@@ -30973,7 +30973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>1241</v>
       </c>
@@ -31011,7 +31011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>1242</v>
       </c>
@@ -31049,7 +31049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>1244</v>
       </c>
@@ -31087,7 +31087,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>1246</v>
       </c>
@@ -31125,7 +31125,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>1247</v>
       </c>
@@ -31163,7 +31163,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>1249</v>
       </c>
@@ -31201,7 +31201,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>1251</v>
       </c>
@@ -31239,7 +31239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>1252</v>
       </c>
@@ -31277,7 +31277,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>1253</v>
       </c>
@@ -31315,7 +31315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>1254</v>
       </c>
@@ -31353,7 +31353,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>1256</v>
       </c>
@@ -31391,7 +31391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>1258</v>
       </c>
@@ -31429,7 +31429,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>1260</v>
       </c>
@@ -31467,7 +31467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>1262</v>
       </c>
@@ -31505,7 +31505,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>1263</v>
       </c>
@@ -31543,7 +31543,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>1264</v>
       </c>
@@ -31581,7 +31581,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>1266</v>
       </c>
@@ -31619,7 +31619,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>1268</v>
       </c>
@@ -31657,7 +31657,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>1270</v>
       </c>
@@ -31695,7 +31695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>1272</v>
       </c>
@@ -31733,7 +31733,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>1274</v>
       </c>
@@ -31771,7 +31771,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>1276</v>
       </c>
@@ -31809,7 +31809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>1277</v>
       </c>
@@ -31847,7 +31847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>1278</v>
       </c>
@@ -31885,7 +31885,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>1280</v>
       </c>
@@ -31923,7 +31923,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>1282</v>
       </c>
@@ -31961,7 +31961,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>1283</v>
       </c>
@@ -31999,7 +31999,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>1285</v>
       </c>
@@ -32037,7 +32037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>1287</v>
       </c>
@@ -32075,7 +32075,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>1288</v>
       </c>
@@ -32113,7 +32113,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>1290</v>
       </c>
@@ -32151,7 +32151,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>1292</v>
       </c>
@@ -32189,7 +32189,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>1293</v>
       </c>
@@ -32227,7 +32227,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>1295</v>
       </c>
@@ -32265,7 +32265,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>1296</v>
       </c>
@@ -32303,7 +32303,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>1297</v>
       </c>
@@ -32341,7 +32341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>1299</v>
       </c>
@@ -32379,7 +32379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>1301</v>
       </c>
@@ -32417,7 +32417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>1302</v>
       </c>
@@ -32455,7 +32455,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>1304</v>
       </c>
@@ -32493,7 +32493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>1305</v>
       </c>
@@ -32531,7 +32531,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>1306</v>
       </c>
@@ -32569,7 +32569,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>1308</v>
       </c>
@@ -32607,7 +32607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>1310</v>
       </c>
@@ -32645,7 +32645,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>1312</v>
       </c>
@@ -32683,7 +32683,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>1314</v>
       </c>
@@ -32721,7 +32721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>1315</v>
       </c>
@@ -32759,7 +32759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>1317</v>
       </c>
@@ -32797,7 +32797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>1319</v>
       </c>
@@ -32835,7 +32835,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>1321</v>
       </c>
@@ -32873,7 +32873,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>1322</v>
       </c>
@@ -32911,7 +32911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>1324</v>
       </c>
@@ -32949,7 +32949,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>1326</v>
       </c>
@@ -32987,7 +32987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>1327</v>
       </c>
@@ -33025,7 +33025,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>1328</v>
       </c>
@@ -33063,7 +33063,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>1329</v>
       </c>
@@ -33101,7 +33101,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>1330</v>
       </c>
@@ -33139,7 +33139,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>1332</v>
       </c>
@@ -33177,7 +33177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>1333</v>
       </c>
@@ -33215,7 +33215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>1334</v>
       </c>
@@ -33253,7 +33253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>1336</v>
       </c>
@@ -33291,7 +33291,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>1338</v>
       </c>
@@ -33329,7 +33329,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>1340</v>
       </c>
@@ -33367,7 +33367,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>1341</v>
       </c>
@@ -33405,7 +33405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>1342</v>
       </c>
@@ -33443,7 +33443,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>1343</v>
       </c>
@@ -33481,7 +33481,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>1345</v>
       </c>
@@ -33519,7 +33519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>1347</v>
       </c>
@@ -33557,7 +33557,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>1348</v>
       </c>
@@ -33595,7 +33595,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>1350</v>
       </c>
@@ -33633,7 +33633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>1351</v>
       </c>
@@ -33671,7 +33671,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>1353</v>
       </c>
@@ -33709,7 +33709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>1354</v>
       </c>
@@ -33747,7 +33747,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>1355</v>
       </c>
@@ -33785,7 +33785,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>1357</v>
       </c>
@@ -33823,7 +33823,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>1359</v>
       </c>
@@ -33861,7 +33861,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>1361</v>
       </c>
@@ -33899,7 +33899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>1363</v>
       </c>
@@ -33937,7 +33937,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>1365</v>
       </c>
@@ -33975,7 +33975,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>1366</v>
       </c>
@@ -34013,7 +34013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>1367</v>
       </c>
@@ -34051,7 +34051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>1368</v>
       </c>
@@ -34089,7 +34089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>1369</v>
       </c>
@@ -34127,7 +34127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>1371</v>
       </c>
@@ -34165,7 +34165,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>1373</v>
       </c>
@@ -34203,7 +34203,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>1374</v>
       </c>
@@ -34241,7 +34241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>1376</v>
       </c>
@@ -34279,7 +34279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>1378</v>
       </c>
@@ -34317,7 +34317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>1380</v>
       </c>
@@ -34355,7 +34355,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>1381</v>
       </c>
@@ -34393,7 +34393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>1382</v>
       </c>
@@ -34431,7 +34431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>1383</v>
       </c>
@@ -34469,7 +34469,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>1384</v>
       </c>
@@ -34507,7 +34507,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>1385</v>
       </c>
@@ -34545,7 +34545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>1387</v>
       </c>
@@ -34583,7 +34583,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>1389</v>
       </c>
@@ -34621,7 +34621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>1390</v>
       </c>
@@ -34659,7 +34659,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>1392</v>
       </c>
@@ -34697,7 +34697,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>1393</v>
       </c>
@@ -34735,7 +34735,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>1394</v>
       </c>
@@ -34773,7 +34773,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>1396</v>
       </c>
@@ -34811,7 +34811,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>1398</v>
       </c>
@@ -34849,7 +34849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>1400</v>
       </c>
@@ -34887,7 +34887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>1401</v>
       </c>
@@ -34925,7 +34925,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>1403</v>
       </c>
@@ -34963,7 +34963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>1405</v>
       </c>
@@ -35001,7 +35001,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>1407</v>
       </c>
@@ -35039,7 +35039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>1409</v>
       </c>
@@ -35077,7 +35077,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>1410</v>
       </c>
@@ -35115,7 +35115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>1412</v>
       </c>
@@ -35153,7 +35153,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>1413</v>
       </c>
@@ -35191,7 +35191,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>1415</v>
       </c>
@@ -35229,7 +35229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>1416</v>
       </c>
@@ -35267,7 +35267,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>1418</v>
       </c>
@@ -35305,7 +35305,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>1419</v>
       </c>
@@ -35343,7 +35343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>1421</v>
       </c>
@@ -35381,7 +35381,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>1423</v>
       </c>
@@ -35419,7 +35419,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>1424</v>
       </c>
@@ -35457,7 +35457,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>1425</v>
       </c>
@@ -35495,7 +35495,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="785" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>1427</v>
       </c>
@@ -35533,7 +35533,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="786" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>1428</v>
       </c>
@@ -35571,7 +35571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>1429</v>
       </c>
@@ -35609,7 +35609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>1431</v>
       </c>
@@ -35647,7 +35647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>1433</v>
       </c>
@@ -35685,7 +35685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="790" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>1435</v>
       </c>
@@ -35723,7 +35723,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="791" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>1437</v>
       </c>
@@ -35761,7 +35761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="792" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>1439</v>
       </c>
@@ -35799,7 +35799,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="793" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>1440</v>
       </c>
@@ -35837,7 +35837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="794" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>1442</v>
       </c>
@@ -35875,7 +35875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="795" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>1444</v>
       </c>
@@ -35913,7 +35913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="796" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>1446</v>
       </c>
@@ -35951,7 +35951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="797" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>1448</v>
       </c>
@@ -35989,7 +35989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="798" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>1449</v>
       </c>
@@ -36027,7 +36027,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="799" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>1451</v>
       </c>
@@ -36065,7 +36065,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="800" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>1453</v>
       </c>
@@ -36103,7 +36103,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="801" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>1454</v>
       </c>
@@ -36141,7 +36141,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="802" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>1456</v>
       </c>
@@ -36179,7 +36179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="803" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>1458</v>
       </c>
@@ -36217,7 +36217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="804" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>1460</v>
       </c>
@@ -36255,7 +36255,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="805" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>1462</v>
       </c>
@@ -36293,7 +36293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="806" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>1463</v>
       </c>
@@ -36331,7 +36331,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="807" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>1465</v>
       </c>
@@ -36369,7 +36369,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="808" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>1467</v>
       </c>
@@ -36407,7 +36407,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="809" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>1468</v>
       </c>
@@ -36445,7 +36445,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="810" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>1469</v>
       </c>
@@ -36483,7 +36483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="811" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>1470</v>
       </c>
@@ -36521,7 +36521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="812" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>1471</v>
       </c>
@@ -36559,7 +36559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="813" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>1472</v>
       </c>
@@ -36597,7 +36597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="814" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>1474</v>
       </c>
@@ -36635,7 +36635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="815" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>1475</v>
       </c>
@@ -36673,7 +36673,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="816" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>1477</v>
       </c>
@@ -36711,7 +36711,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="817" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>1479</v>
       </c>
@@ -36749,7 +36749,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="818" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>1480</v>
       </c>
@@ -36787,7 +36787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="819" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>1482</v>
       </c>
@@ -36825,7 +36825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="820" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>1483</v>
       </c>
@@ -36863,7 +36863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="821" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>1484</v>
       </c>
@@ -36901,7 +36901,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="822" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>1486</v>
       </c>
@@ -36939,7 +36939,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="823" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>1488</v>
       </c>
@@ -36977,7 +36977,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="824" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>1489</v>
       </c>
@@ -37015,7 +37015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="825" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>1490</v>
       </c>
@@ -37053,7 +37053,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="826" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>1491</v>
       </c>
@@ -37091,7 +37091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="827" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>1493</v>
       </c>
@@ -37129,7 +37129,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="828" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>1495</v>
       </c>
@@ -37167,7 +37167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="829" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>1496</v>
       </c>
@@ -37205,7 +37205,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="830" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>1497</v>
       </c>
@@ -37243,7 +37243,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="831" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>1499</v>
       </c>
@@ -37281,7 +37281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="832" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>1500</v>
       </c>
@@ -37319,7 +37319,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>1501</v>
       </c>
@@ -37357,7 +37357,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="834" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>1502</v>
       </c>
@@ -37395,7 +37395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="835" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>1503</v>
       </c>
@@ -37433,7 +37433,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="836" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>1505</v>
       </c>
@@ -37471,7 +37471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="837" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>1506</v>
       </c>
@@ -37509,7 +37509,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="838" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>1507</v>
       </c>
@@ -37547,7 +37547,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="839" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>1508</v>
       </c>
@@ -37585,7 +37585,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="840" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>1509</v>
       </c>
@@ -37623,7 +37623,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="841" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>1511</v>
       </c>
@@ -37661,7 +37661,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="842" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>1512</v>
       </c>
@@ -37699,7 +37699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="843" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>1514</v>
       </c>
@@ -37737,7 +37737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="844" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>1516</v>
       </c>
@@ -37775,7 +37775,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="845" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>1518</v>
       </c>
@@ -37813,7 +37813,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="846" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>1519</v>
       </c>
@@ -37851,7 +37851,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="847" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>1521</v>
       </c>
@@ -37889,7 +37889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="848" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>1522</v>
       </c>
@@ -37927,7 +37927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="849" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>1523</v>
       </c>
@@ -37965,7 +37965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="850" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>1525</v>
       </c>
@@ -38003,7 +38003,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="851" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
         <v>1526</v>
       </c>
@@ -38041,7 +38041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="852" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>1527</v>
       </c>
@@ -38079,7 +38079,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="853" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
         <v>1529</v>
       </c>
@@ -38117,7 +38117,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="854" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>1531</v>
       </c>
@@ -38155,7 +38155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="855" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>1533</v>
       </c>
@@ -38193,7 +38193,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="856" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>1535</v>
       </c>
@@ -38231,7 +38231,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="857" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>1537</v>
       </c>
@@ -38269,7 +38269,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="858" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
         <v>1539</v>
       </c>
@@ -38307,7 +38307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="859" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>1541</v>
       </c>
@@ -38345,7 +38345,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="860" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>1543</v>
       </c>
@@ -38383,7 +38383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="861" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>1545</v>
       </c>
@@ -38421,7 +38421,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="862" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>1546</v>
       </c>
@@ -38459,7 +38459,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="863" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
         <v>1547</v>
       </c>
@@ -38497,7 +38497,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="864" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
         <v>1549</v>
       </c>
@@ -38535,7 +38535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="865" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
         <v>1550</v>
       </c>
@@ -38573,7 +38573,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="866" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
         <v>1551</v>
       </c>
@@ -38611,7 +38611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="867" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
         <v>1552</v>
       </c>
@@ -38649,7 +38649,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="868" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
         <v>1554</v>
       </c>
@@ -38687,7 +38687,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="869" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
         <v>1556</v>
       </c>
@@ -38725,7 +38725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="870" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
         <v>1558</v>
       </c>
@@ -38763,7 +38763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="871" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
         <v>1559</v>
       </c>
@@ -38801,7 +38801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="872" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
         <v>1560</v>
       </c>
@@ -38839,7 +38839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="873" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
         <v>1561</v>
       </c>
@@ -38877,7 +38877,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="874" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
         <v>1563</v>
       </c>
@@ -38915,7 +38915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="875" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
         <v>1565</v>
       </c>
@@ -38953,7 +38953,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="876" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
         <v>1566</v>
       </c>
@@ -38991,7 +38991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="877" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
         <v>1568</v>
       </c>
@@ -39029,7 +39029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="878" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
         <v>1569</v>
       </c>
@@ -39067,7 +39067,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="879" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
         <v>1571</v>
       </c>
@@ -39105,7 +39105,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="880" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
         <v>1572</v>
       </c>
@@ -39143,7 +39143,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="881" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
         <v>1573</v>
       </c>
@@ -39181,7 +39181,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="882" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
         <v>1574</v>
       </c>
@@ -39219,7 +39219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="883" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
         <v>1576</v>
       </c>
@@ -39257,7 +39257,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="884" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
         <v>1577</v>
       </c>
@@ -39295,7 +39295,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="885" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
         <v>1579</v>
       </c>
@@ -39333,7 +39333,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="886" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
         <v>1581</v>
       </c>
@@ -39371,7 +39371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="887" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
         <v>1583</v>
       </c>
@@ -39409,7 +39409,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="888" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
         <v>1585</v>
       </c>
@@ -39447,7 +39447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="889" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
         <v>1586</v>
       </c>
@@ -39485,7 +39485,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="890" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
         <v>1588</v>
       </c>
@@ -39523,7 +39523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="891" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
         <v>1590</v>
       </c>
@@ -39561,7 +39561,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="892" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
         <v>1592</v>
       </c>
@@ -39599,7 +39599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="893" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
         <v>1594</v>
       </c>
@@ -39637,7 +39637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="894" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
         <v>1596</v>
       </c>
@@ -39675,7 +39675,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="895" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
         <v>1597</v>
       </c>
@@ -39713,7 +39713,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="896" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
         <v>1598</v>
       </c>
@@ -39751,7 +39751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="897" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>1599</v>
       </c>
@@ -39789,7 +39789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="898" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>1600</v>
       </c>
@@ -39827,7 +39827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="899" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>1601</v>
       </c>
@@ -39865,7 +39865,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="900" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>1603</v>
       </c>
@@ -39903,7 +39903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="901" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>1604</v>
       </c>
@@ -39941,7 +39941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="902" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>1605</v>
       </c>
@@ -39979,7 +39979,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="903" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>1607</v>
       </c>
@@ -40017,7 +40017,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="904" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>1608</v>
       </c>
@@ -40055,7 +40055,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="905" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
         <v>1610</v>
       </c>
@@ -40093,7 +40093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="906" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
         <v>1611</v>
       </c>
@@ -40131,7 +40131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="907" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
         <v>1612</v>
       </c>
@@ -40169,7 +40169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="908" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
         <v>1614</v>
       </c>
@@ -40207,7 +40207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="909" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
         <v>1615</v>
       </c>
@@ -40245,7 +40245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="910" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
         <v>1617</v>
       </c>
@@ -40283,7 +40283,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="911" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
         <v>1618</v>
       </c>
@@ -40321,7 +40321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="912" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
         <v>1620</v>
       </c>
@@ -40359,7 +40359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="913" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
         <v>1621</v>
       </c>
@@ -40397,7 +40397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="914" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A914" t="s">
         <v>1623</v>
       </c>
@@ -40435,7 +40435,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="915" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A915" t="s">
         <v>1625</v>
       </c>
@@ -40473,7 +40473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="916" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A916" t="s">
         <v>1626</v>
       </c>
@@ -40511,7 +40511,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="917" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
         <v>1627</v>
       </c>
@@ -40549,7 +40549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="918" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A918" t="s">
         <v>1629</v>
       </c>
@@ -40587,7 +40587,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="919" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
         <v>1630</v>
       </c>
@@ -40625,7 +40625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="920" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
         <v>1631</v>
       </c>
@@ -40663,7 +40663,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="921" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
         <v>1633</v>
       </c>
@@ -40701,7 +40701,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="922" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
         <v>1634</v>
       </c>
@@ -40739,7 +40739,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="923" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
         <v>1636</v>
       </c>
@@ -40777,7 +40777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="924" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
         <v>1638</v>
       </c>
@@ -40815,7 +40815,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="925" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
         <v>1640</v>
       </c>
@@ -40853,7 +40853,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="926" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
         <v>1641</v>
       </c>
@@ -40891,7 +40891,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="927" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
         <v>1643</v>
       </c>
@@ -40929,7 +40929,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="928" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
         <v>1644</v>
       </c>
@@ -40967,7 +40967,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="929" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
         <v>1645</v>
       </c>
@@ -41005,7 +41005,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="930" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
         <v>1647</v>
       </c>
@@ -41043,7 +41043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="931" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
         <v>1649</v>
       </c>
@@ -41081,7 +41081,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="932" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
         <v>1650</v>
       </c>
@@ -41119,7 +41119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="933" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
         <v>1651</v>
       </c>
@@ -41157,7 +41157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="934" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
         <v>1653</v>
       </c>
@@ -41195,7 +41195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="935" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
         <v>1654</v>
       </c>
@@ -41233,7 +41233,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="936" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
         <v>1656</v>
       </c>
@@ -41271,7 +41271,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="937" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
         <v>1657</v>
       </c>
@@ -41309,7 +41309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="938" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
         <v>1659</v>
       </c>
@@ -41347,7 +41347,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="939" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
         <v>1660</v>
       </c>
@@ -41385,7 +41385,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="940" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
         <v>1661</v>
       </c>
@@ -41423,7 +41423,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="941" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
         <v>1662</v>
       </c>
@@ -41461,7 +41461,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="942" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
         <v>1664</v>
       </c>
@@ -41499,7 +41499,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="943" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
         <v>1666</v>
       </c>
@@ -41537,7 +41537,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="944" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
         <v>1667</v>
       </c>
@@ -41575,7 +41575,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="945" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
         <v>1669</v>
       </c>
@@ -41613,7 +41613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="946" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
         <v>1671</v>
       </c>
@@ -41651,7 +41651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="947" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
         <v>1672</v>
       </c>
@@ -41689,7 +41689,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="948" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
         <v>1674</v>
       </c>
@@ -41727,7 +41727,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="949" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
         <v>1676</v>
       </c>
@@ -41765,7 +41765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="950" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
         <v>1677</v>
       </c>
@@ -41803,7 +41803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="951" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
         <v>1678</v>
       </c>
@@ -41841,7 +41841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="952" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
         <v>1679</v>
       </c>
@@ -41879,7 +41879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="953" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
         <v>1681</v>
       </c>
@@ -41917,7 +41917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="954" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
         <v>1683</v>
       </c>
@@ -41955,7 +41955,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="955" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
         <v>1685</v>
       </c>
@@ -41993,7 +41993,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="956" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
         <v>1686</v>
       </c>
@@ -42031,7 +42031,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="957" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
         <v>1688</v>
       </c>
@@ -42069,7 +42069,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="958" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
         <v>1689</v>
       </c>
@@ -42107,7 +42107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="959" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
         <v>1690</v>
       </c>
@@ -42145,7 +42145,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="960" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
         <v>1691</v>
       </c>
@@ -42183,7 +42183,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="961" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
         <v>1693</v>
       </c>
@@ -42221,7 +42221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="962" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
         <v>1695</v>
       </c>
@@ -42259,7 +42259,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="963" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
         <v>1696</v>
       </c>
@@ -42297,7 +42297,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="964" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
         <v>1698</v>
       </c>
@@ -42335,7 +42335,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="965" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
         <v>1699</v>
       </c>
@@ -42373,7 +42373,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="966" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
         <v>1700</v>
       </c>
@@ -42411,7 +42411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="967" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
         <v>1701</v>
       </c>
@@ -42449,7 +42449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="968" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
         <v>1703</v>
       </c>
@@ -42487,7 +42487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="969" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
         <v>1704</v>
       </c>
@@ -42525,7 +42525,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="970" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
         <v>1705</v>
       </c>
@@ -42563,7 +42563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="971" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
         <v>1706</v>
       </c>
@@ -42601,7 +42601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="972" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
         <v>1707</v>
       </c>
@@ -42639,7 +42639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="973" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
         <v>1709</v>
       </c>
@@ -42677,7 +42677,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="974" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
         <v>1710</v>
       </c>
@@ -42715,7 +42715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="975" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
         <v>1712</v>
       </c>
@@ -42753,7 +42753,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="976" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
         <v>1714</v>
       </c>
@@ -42791,7 +42791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="977" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
         <v>1716</v>
       </c>
@@ -42829,7 +42829,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="978" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
         <v>1718</v>
       </c>
@@ -42867,7 +42867,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="979" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
         <v>1719</v>
       </c>
@@ -42905,7 +42905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="980" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
         <v>1720</v>
       </c>
@@ -42943,7 +42943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="981" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
         <v>1721</v>
       </c>
@@ -42981,7 +42981,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="982" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
         <v>1722</v>
       </c>
@@ -43019,7 +43019,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="983" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
         <v>1724</v>
       </c>
@@ -43057,7 +43057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="984" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
         <v>1725</v>
       </c>
@@ -43095,7 +43095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="985" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
         <v>1727</v>
       </c>
@@ -43133,7 +43133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="986" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
         <v>1728</v>
       </c>
@@ -43171,7 +43171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="987" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
         <v>1729</v>
       </c>
@@ -43209,7 +43209,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="988" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
         <v>1731</v>
       </c>
@@ -43247,7 +43247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="989" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A989" t="s">
         <v>1732</v>
       </c>
@@ -43285,7 +43285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="990" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
         <v>1733</v>
       </c>
@@ -43323,7 +43323,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="991" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
         <v>1734</v>
       </c>
@@ -43361,7 +43361,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="992" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
         <v>1736</v>
       </c>
@@ -43399,7 +43399,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="993" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
         <v>1738</v>
       </c>
@@ -43437,7 +43437,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="994" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
         <v>1739</v>
       </c>
@@ -43475,7 +43475,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="995" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A995" t="s">
         <v>1740</v>
       </c>
@@ -43513,7 +43513,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="996" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
         <v>1741</v>
       </c>
@@ -43551,7 +43551,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="997" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
         <v>1742</v>
       </c>
@@ -43589,7 +43589,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="998" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
         <v>1743</v>
       </c>
@@ -43627,7 +43627,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="999" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
         <v>1745</v>
       </c>
@@ -43665,7 +43665,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1000" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1000" t="s">
         <v>1746</v>
       </c>
@@ -43703,7 +43703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1001" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1001" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
         <v>1748</v>
       </c>
